--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3174,13 +3174,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
+    <row r="43" ht="90" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -3190,37 +3190,37 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
@@ -3230,22 +3230,22 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -3255,37 +3255,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
@@ -3300,55 +3300,59 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="60" customHeight="1">
+          <t>16a26b201</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-3</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr"/>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Trivial.</t>
+        </is>
+      </c>
       <c r="K45" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3361,17 +3365,17 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="75" customHeight="1">
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
@@ -3386,17 +3390,17 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3406,14 +3410,10 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3426,17 +3426,17 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="75" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -3446,22 +3446,22 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3471,10 +3471,14 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr"/>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K47" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3487,17 +3491,17 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="75" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -3507,22 +3511,22 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3532,14 +3536,10 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3552,17 +3552,17 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="45" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="75" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -3572,37 +3572,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
     </row>
@@ -3627,47 +3627,47 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>OPS-5</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: persistence works; no silent overwrites.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
@@ -3680,7 +3680,11 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="45" customHeight="1">
       <c r="A51" s="2" t="n">
@@ -3688,7 +3692,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -3703,32 +3707,32 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
@@ -3749,55 +3753,59 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M52" s="3" t="inlineStr"/>
     </row>
     <row r="53" ht="45" customHeight="1">
@@ -3806,7 +3814,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -3816,33 +3824,37 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>@media (min-width: 768px) and (max-width: 1024px) breakpoint. Collapse sidebar to top nav, stack KPI tiles 2-up, ensure tabs scroll horizontally.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr"/>
+          <t>5 min after answer</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Win: -671 lines.</t>
+        </is>
+      </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Deferred — desktop is primary use case.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -3859,7 +3871,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -3874,28 +3886,28 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Full mobile pass: hamburger nav, single-column stacking, ≥44px tap targets, swipe sub-tabs, condensed tables.</t>
+          <t>@media (min-width: 768px) and (max-width: 1024px) breakpoint. Collapse sidebar to top nav, stack KPI tiles 2-up, ensure tabs scroll horizontally.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Deferred indefinitely.</t>
+          <t>Deferred — desktop is primary use case.</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -3912,7 +3924,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -3922,37 +3934,33 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Full mobile pass: hamburger nav, single-column stacking, ≥44px tap targets, swipe sub-tabs, condensed tables.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Deferred indefinitely.</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -3969,56 +3977,174 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K56" s="14" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K57" s="14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K58" s="14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4116,13 +4242,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="17" t="n">
         <v>5</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -4173,13 +4299,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="22" t="n">
         <v>14</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,10 @@
     <font>
       <name val="Menlo"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Menlo"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -175,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -192,11 +196,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -204,37 +211,37 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -608,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -624,6 +631,7 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -692,6 +700,11 @@
           <t>Commit</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>How to Test</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -749,6 +762,11 @@
       </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -806,6 +824,11 @@
       </c>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -863,6 +886,11 @@
       </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -873,7 +901,7 @@
           <t>CLEAN-1</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -920,6 +948,11 @@
       </c>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -930,7 +963,7 @@
           <t>CLEAN-3</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -977,6 +1010,11 @@
       </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -987,7 +1025,7 @@
           <t>OPS-1</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1034,6 +1072,11 @@
       </c>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1044,7 +1087,7 @@
           <t>PERF-6</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1087,6 +1130,11 @@
       </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -1097,7 +1145,7 @@
           <t>PERF-7</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1144,6 +1192,11 @@
       </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -1154,7 +1207,7 @@
           <t>QUANT-3</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1197,6 +1250,11 @@
       </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -1207,7 +1265,7 @@
           <t>QUANT-4</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1254,6 +1312,11 @@
       </c>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1264,7 +1327,7 @@
           <t>QUANT-5</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1311,6 +1374,11 @@
       </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="n">
@@ -1321,7 +1389,7 @@
           <t>QUANT-6</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1364,6 +1432,11 @@
       </c>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -1374,7 +1447,7 @@
           <t>MOD-2</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1417,6 +1490,11 @@
       </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="n">
@@ -1427,7 +1505,7 @@
           <t>CLEAN-4</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1474,6 +1552,11 @@
       </c>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -1484,7 +1567,7 @@
           <t>OPS-2</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1527,6 +1610,11 @@
       </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1537,7 +1625,7 @@
           <t>OPS-3</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1580,6 +1668,11 @@
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -1590,7 +1683,7 @@
           <t>OPS-4</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1633,6 +1726,11 @@
       </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -1643,7 +1741,7 @@
           <t>MOD-1</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1690,6 +1788,11 @@
       </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -1740,13 +1843,18 @@
           <t>Concerning: 30+ min into backtest, still 0 BUYs across 5 months simulated. Likely needs per-band kill (TC at score 60-79 only) instead of full kill.</t>
         </is>
       </c>
-      <c r="K20" s="10" t="inlineStr">
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -1757,7 +1865,7 @@
           <t>A5-followup</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1797,7 +1905,7 @@
           <t>Wilson LB clears 40% threshold. Don't enable until subtype investigation done.</t>
         </is>
       </c>
-      <c r="K21" s="10" t="inlineStr">
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
         </is>
@@ -1806,6 +1914,11 @@
       <c r="M21" s="3" t="inlineStr">
         <is>
           <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>grep -A20 'pullback_bull_701' config/config.json → _validations entry present with n=134 wr_lb=0.446. _enabled stays false.</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1971,7 @@
           <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K22" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1871,6 +1984,11 @@
       <c r="M22" s="3" t="inlineStr">
         <is>
           <t>2c9b9f339</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
         </is>
       </c>
     </row>
@@ -1923,7 +2041,7 @@
           <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1936,6 +2054,11 @@
       <c r="M23" s="3" t="inlineStr">
         <is>
           <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2111,7 @@
           <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2001,6 +2124,11 @@
       <c r="M24" s="3" t="inlineStr">
         <is>
           <t>0574c60d4</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2181,7 @@
           <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2066,6 +2194,11 @@
       <c r="M25" s="3" t="inlineStr">
         <is>
           <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2251,7 @@
           <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="K26" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2131,6 +2264,11 @@
       <c r="M26" s="3" t="inlineStr">
         <is>
           <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2321,7 @@
           <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K27" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2196,6 +2334,11 @@
       <c r="M27" s="3" t="inlineStr">
         <is>
           <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2391,7 @@
           <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2261,6 +2404,11 @@
       <c r="M28" s="3" t="inlineStr">
         <is>
           <t>f35f0c124</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2461,7 @@
           <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K29" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2326,6 +2474,11 @@
       <c r="M29" s="3" t="inlineStr">
         <is>
           <t>fc76c9ec8 + 6ceca2d18</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2531,7 @@
           <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="K30" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2391,6 +2544,11 @@
       <c r="M30" s="3" t="inlineStr">
         <is>
           <t>fc76c9ec8</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2601,7 @@
           <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="K31" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2456,6 +2614,11 @@
       <c r="M31" s="3" t="inlineStr">
         <is>
           <t>3d4eb71d7</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2671,7 @@
           <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2521,6 +2684,11 @@
       <c r="M32" s="3" t="inlineStr">
         <is>
           <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2741,7 @@
           <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="K33" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2586,6 +2754,11 @@
       <c r="M33" s="3" t="inlineStr">
         <is>
           <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2771,7 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2638,7 +2811,7 @@
           <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="K34" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2651,6 +2824,11 @@
       <c r="M34" s="3" t="inlineStr">
         <is>
           <t>9bc015562</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2841,7 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2703,7 +2881,7 @@
           <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr">
+      <c r="K35" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2716,6 +2894,11 @@
       <c r="M35" s="3" t="inlineStr">
         <is>
           <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2911,7 @@
           <t>F11</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2768,7 +2951,7 @@
           <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="K36" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2781,6 +2964,11 @@
       <c r="M36" s="3" t="inlineStr">
         <is>
           <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2981,7 @@
           <t>PERF-4</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2833,7 +3021,7 @@
           <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="K37" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2846,6 +3034,11 @@
       <c r="M37" s="3" t="inlineStr">
         <is>
           <t>2eb4e3b3d</t>
+        </is>
+      </c>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -2858,7 +3051,7 @@
           <t>PERF-5</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2898,7 +3091,7 @@
           <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr">
+      <c r="K38" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2911,6 +3104,11 @@
       <c r="M38" s="3" t="inlineStr">
         <is>
           <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N38" s="8" t="inlineStr">
+        <is>
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
         </is>
       </c>
     </row>
@@ -2923,7 +3121,7 @@
           <t>A5</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2963,7 +3161,7 @@
           <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr">
+      <c r="K39" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2976,6 +3174,11 @@
       <c r="M39" s="3" t="inlineStr">
         <is>
           <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
         </is>
       </c>
     </row>
@@ -2988,7 +3191,7 @@
           <t>K1</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3028,7 +3231,7 @@
           <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr">
+      <c r="K40" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3041,6 +3244,11 @@
       <c r="M40" s="3" t="inlineStr">
         <is>
           <t>3d4eb71d7</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3261,7 @@
           <t>K2</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3093,7 +3301,7 @@
           <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="K41" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3106,6 +3314,11 @@
       <c r="M41" s="3" t="inlineStr">
         <is>
           <t>3d4eb71d7</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3331,7 @@
           <t>K5</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3158,7 +3371,7 @@
           <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
-      <c r="K42" s="11" t="inlineStr">
+      <c r="K42" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3171,6 +3384,11 @@
       <c r="M42" s="3" t="inlineStr">
         <is>
           <t>302e9ea00</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3401,7 @@
           <t>K4</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3223,7 +3441,7 @@
           <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
+      <c r="K43" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3236,6 +3454,11 @@
       <c r="M43" s="3" t="inlineStr">
         <is>
           <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3471,7 @@
           <t>A7</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3288,7 +3511,7 @@
           <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
-      <c r="K44" s="11" t="inlineStr">
+      <c r="K44" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3301,6 +3524,11 @@
       <c r="M44" s="3" t="inlineStr">
         <is>
           <t>16a26b201</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3541,7 @@
           <t>MOD-3</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3353,7 +3581,7 @@
           <t>Trivial.</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="K45" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3366,6 +3594,11 @@
       <c r="M45" s="3" t="inlineStr">
         <is>
           <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3611,7 @@
           <t>J1</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3414,7 +3647,7 @@
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="11" t="inlineStr">
+      <c r="K46" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3427,6 +3660,11 @@
       <c r="M46" s="3" t="inlineStr">
         <is>
           <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3677,7 @@
           <t>J2</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3479,7 +3717,7 @@
           <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
+      <c r="K47" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3492,6 +3730,11 @@
       <c r="M47" s="3" t="inlineStr">
         <is>
           <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N47" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3747,7 @@
           <t>J3</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3540,7 +3783,7 @@
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="11" t="inlineStr">
+      <c r="K48" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3553,6 +3796,11 @@
       <c r="M48" s="3" t="inlineStr">
         <is>
           <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N48" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3813,7 @@
           <t>F11-followup</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3605,7 +3853,7 @@
           <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
-      <c r="K49" s="11" t="inlineStr">
+      <c r="K49" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3620,8 +3868,13 @@
           <t>1e40d30fc</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="45" customHeight="1">
+      <c r="N49" s="8" t="inlineStr">
+        <is>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -3630,7 +3883,7 @@
           <t>OPS-5</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3670,7 +3923,7 @@
           <t>Trivial CLI wrapper.</t>
         </is>
       </c>
-      <c r="K50" s="11" t="inlineStr">
+      <c r="K50" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3683,6 +3936,11 @@
       <c r="M50" s="3" t="inlineStr">
         <is>
           <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N50" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3953,7 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3735,7 +3993,7 @@
           <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
-      <c r="K51" s="11" t="inlineStr">
+      <c r="K51" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3746,6 +4004,11 @@
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr"/>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="45" customHeight="1">
       <c r="A52" s="2" t="n">
@@ -3756,7 +4019,7 @@
           <t>I4</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -3796,7 +4059,7 @@
           <t>7 backup dirs present, latest 2026-05-08.</t>
         </is>
       </c>
-      <c r="K52" s="11" t="inlineStr">
+      <c r="K52" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3807,6 +4070,11 @@
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="8" t="inlineStr">
+        <is>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="45" customHeight="1">
       <c r="A53" s="2" t="n">
@@ -3817,7 +4085,7 @@
           <t>CLEAN-2</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3857,13 +4125,18 @@
           <t>Standard data-migration retention practice.</t>
         </is>
       </c>
-      <c r="K53" s="13" t="inlineStr">
+      <c r="K53" s="14" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="45" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -3874,7 +4147,7 @@
           <t>MOB-1</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3910,13 +4183,18 @@
           <t>Deferred — desktop is primary use case.</t>
         </is>
       </c>
-      <c r="K54" s="13" t="inlineStr">
+      <c r="K54" s="14" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="45" customHeight="1">
       <c r="A55" s="2" t="n">
@@ -3927,7 +4205,7 @@
           <t>MOB-2</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -3963,13 +4241,18 @@
           <t>Deferred indefinitely.</t>
         </is>
       </c>
-      <c r="K55" s="13" t="inlineStr">
+      <c r="K55" s="14" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="3" t="inlineStr"/>
+      <c r="N55" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="45" customHeight="1">
       <c r="A56" s="2" t="n">
@@ -3980,7 +4263,7 @@
           <t>PERF-8-13</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4020,13 +4303,18 @@
           <t>Don't pre-implement.</t>
         </is>
       </c>
-      <c r="K56" s="13" t="inlineStr">
+      <c r="K56" s="14" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="3" t="inlineStr"/>
+      <c r="N56" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="2" t="n">
@@ -4077,13 +4365,18 @@
           <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
-      <c r="K57" s="14" t="inlineStr">
+      <c r="K57" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="90" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -4094,7 +4387,7 @@
           <t>H1</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4134,7 +4427,7 @@
           <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
         </is>
       </c>
-      <c r="K58" s="14" t="inlineStr">
+      <c r="K58" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
@@ -4145,6 +4438,11 @@
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr"/>
+      <c r="N58" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4168,143 +4466,143 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="23" t="n">
         <v>57</v>
       </c>
     </row>
@@ -4328,153 +4626,153 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>What it does</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py list</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>Show all items grouped by status</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py list --open</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Show only OPEN / IN_PROGRESS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py done &lt;id&gt;</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Mark item DONE (auto-fills today's date + HEAD commit)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py done &lt;id&gt; --commit abc123 --date 2026-05-09</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Mark DONE with explicit commit/date</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py status &lt;id&gt; IN_PROGRESS</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Set arbitrary status (OPEN/IN_PROGRESS/DONE/DEFERRED/REJECTED)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py add NEW-ID P1 "Section" "Item title" "What" "How"</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Add a new item to the registry</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py xlsx</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Regenerate this Excel from data/open_items.json</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>edit data/open_items.json directly, then run xlsx</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Free-form edits — works too</t>
         </is>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>OPS-1</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -908,37 +908,37 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: cleaner repo.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment.</t>
+          <t>Calendar reminder for 2026-05-16.</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -954,13 +954,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -970,39 +970,35 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>audit_360.py is the biggest single file — start there.</t>
-        </is>
-      </c>
+          <t>Win: -100ms FCP.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1016,13 +1012,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -1032,37 +1028,37 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Win: cleaner repo.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Calendar reminder for 2026-05-16.</t>
+          <t>Biggest lever for next perf sprint.</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1084,7 +1080,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -1094,32 +1090,32 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr"/>
@@ -1136,13 +1132,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="75" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1152,37 +1148,37 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Caveat: exploratory research, not config-tuning.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint.</t>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1198,13 +1194,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1219,27 +1215,27 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr"/>
@@ -1256,13 +1252,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>MOD-2</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1272,39 +1268,35 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Low priority — local cache works for now.</t>
-        </is>
-      </c>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1318,53 +1310,53 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
+          <t>Win: -X lines.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+          <t>Couples with OPS-1.</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1386,45 +1378,49 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>MOD-1</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr"/>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Defer until next major refactor.</t>
+        </is>
+      </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1438,297 +1434,341 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>GATE-1</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Concerning: 30+ min into backtest, still 0 BUYs across 5 months simulated. Likely needs per-band kill (TC at score 60-79 only) instead of full kill.</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>A5-followup</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1 min</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Win: -X lines.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Wilson LB clears 40% threshold. Don't enable until subtype investigation done.</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>1e40d30fc</t>
+        </is>
+      </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>grep -A20 'pullback_bull_701' config/config.json → _validations entry present with n=134 wr_lb=0.446. _enabled stays false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="75" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>OPERATING-MINDSET</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="105" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>0574c60d4</t>
+        </is>
+      </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
         </is>
       </c>
     </row>
@@ -1738,69 +1778,77 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Q1-step1</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Defer until next major refactor.</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>d8c08399b</t>
+        </is>
+      </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1810,125 +1858,137 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Concerning: 30+ min into backtest, still 0 BUYs across 5 months simulated. Likely needs per-band kill (TC at score 60-79 only) instead of full kill.</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>d8c08399b</t>
+        </is>
+      </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step3</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Wilson LB clears 40% threshold. Don't enable until subtype investigation done.</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>grep -A20 'pullback_bull_701' config/config.json → _validations entry present with n=134 wr_lb=0.446. _enabled stays false.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="75" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1938,22 +1998,22 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1963,12 +2023,12 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -1983,22 +2043,22 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2008,22 +2068,22 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2033,12 +2093,12 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2048,27 +2108,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="105" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2078,37 +2138,37 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2123,12 +2183,12 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2198,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2148,37 +2208,37 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2193,22 +2253,22 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2218,37 +2278,37 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2263,22 +2323,22 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2288,37 +2348,37 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2333,62 +2393,62 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="90" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2403,62 +2463,62 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>CLEAN-1</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2468,67 +2528,67 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>CLEAN-3</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2538,52 +2598,52 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2593,12 +2653,12 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2613,12 +2673,12 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
         </is>
       </c>
     </row>
@@ -2628,32 +2688,32 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2663,12 +2723,12 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2683,62 +2743,62 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-4</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2753,22 +2813,22 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -2778,37 +2838,37 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2823,22 +2883,22 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -2848,37 +2908,37 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -2888,17 +2948,17 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2968,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -2918,37 +2978,37 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -2968,17 +3028,17 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="75" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -2988,37 +3048,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3033,22 +3093,22 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -3058,37 +3118,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3103,22 +3163,22 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="75" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -3128,37 +3188,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3173,22 +3233,22 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -3198,37 +3258,37 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3238,17 +3298,17 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3318,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -3268,22 +3328,22 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3293,12 +3353,12 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3313,22 +3373,22 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="75" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3338,37 +3398,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3383,64 +3443,60 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="90" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3448,52 +3504,52 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3503,12 +3559,12 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: clear activation procedure before flipping live.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3523,12 +3579,12 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
         </is>
       </c>
     </row>
@@ -3538,49 +3594,45 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Trivial.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr"/>
       <c r="K45" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3593,22 +3645,22 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="60" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="75" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -3618,22 +3670,22 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3643,10 +3695,14 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr"/>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>User can still bypass with --no-verify in emergencies.</t>
+        </is>
+      </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3664,17 +3720,17 @@
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="75" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -3684,37 +3740,37 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
@@ -3724,27 +3780,27 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="45" customHeight="1">
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -3754,35 +3810,39 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr"/>
+          <t>Win: safer registry edits + audit trail.</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+        </is>
+      </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3790,27 +3850,27 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="75" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -3820,37 +3880,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3860,17 +3920,17 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
         </is>
       </c>
     </row>
@@ -4502,13 +4562,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -4540,13 +4600,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -1496,13 +1496,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="90" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1512,37 +1512,33 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Wilson LB clears 40% threshold. Don't enable until subtype investigation done.</t>
+          <t>Initial CSS shipped 2026-05-10. May need follow-up for specific tabs (Portfolio, Tracking) once tested live.</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
@@ -1551,14 +1547,10 @@
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>grep -A20 'pullback_bull_701' config/config.json → _validations entry present with n=134 wr_lb=0.446. _enabled stays false.</t>
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
         </is>
       </c>
     </row>
@@ -1568,147 +1560,131 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>MOB-2</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>2c9b9f339</t>
-        </is>
-      </c>
+          <t>Hamburger nav + swipe gestures NOT yet — desktop-style topnav with horizontal scroll works on phones. Revisit only if user reports usability issue.</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>A5-followup</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>Wilson LB clears 40% threshold. Don't enable until subtype investigation done.</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="105" customHeight="1">
+          <t>grep -A20 'pullback_bull_701' config/config.json → _validations entry present with n=134 wr_lb=0.446. _enabled stays false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="75" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1718,22 +1694,22 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1743,12 +1719,12 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1763,22 +1739,22 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>2c9b9f339</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1788,37 +1764,37 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1828,27 +1804,27 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="105" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1858,37 +1834,37 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1903,22 +1879,22 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1933,32 +1909,32 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -1978,17 +1954,17 @@
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1998,37 +1974,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2043,12 +2019,12 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2034,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2068,37 +2044,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2113,22 +2089,22 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2138,37 +2114,37 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2183,22 +2159,22 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2208,22 +2184,22 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2233,12 +2209,12 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2253,22 +2229,22 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2278,37 +2254,37 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2323,12 +2299,12 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2314,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2348,22 +2324,22 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2373,12 +2349,12 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2393,12 +2369,12 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
         </is>
       </c>
     </row>
@@ -2408,47 +2384,47 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2463,12 +2439,12 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2478,47 +2454,47 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2528,27 +2504,27 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="90" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -2558,37 +2534,37 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2598,27 +2574,27 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -2628,37 +2604,37 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2668,27 +2644,27 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -2698,37 +2674,37 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2738,17 +2714,17 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2734,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -2768,37 +2744,37 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2813,22 +2789,22 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -2838,37 +2814,37 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2883,22 +2859,22 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -2908,37 +2884,37 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -2948,27 +2924,27 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -2978,37 +2954,37 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3023,22 +2999,22 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="75" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -3048,37 +3024,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3088,17 +3064,17 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3084,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -3118,37 +3094,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3163,12 +3139,12 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3154,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -3188,22 +3164,22 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3213,12 +3189,12 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3233,22 +3209,22 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="90" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -3258,37 +3234,37 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3298,27 +3274,27 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="75" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -3328,22 +3304,22 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3353,12 +3329,12 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3373,22 +3349,22 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="90" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3398,37 +3374,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3438,17 +3414,17 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -3458,32 +3434,32 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3493,10 +3469,14 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr"/>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+        </is>
+      </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3509,62 +3489,62 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="75" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-3</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3579,22 +3559,22 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -3604,22 +3584,22 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3629,7 +3609,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
+          <t>Win: future Claude sessions discover new tools.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr"/>
@@ -3645,12 +3625,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3640,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -3670,22 +3650,22 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3695,12 +3675,12 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: clear activation procedure before flipping live.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3715,22 +3695,22 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="60" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -3740,39 +3720,35 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3780,27 +3756,27 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="60" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="75" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -3810,37 +3786,37 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -3850,17 +3826,17 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3846,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -3885,32 +3861,32 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3930,7 +3906,7 @@
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3916,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -3955,32 +3931,32 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -3990,67 +3966,67 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>OPS-4</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: persistence works; no silent overwrites.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -4060,63 +4036,67 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>OPS-5</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -4129,10 +4109,14 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
         </is>
       </c>
     </row>
@@ -4142,59 +4126,63 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K53" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr"/>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -4204,55 +4192,63 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>@media (min-width: 768px) and (max-width: 1024px) breakpoint. Collapse sidebar to top nav, stack KPI tiles 2-up, ensure tabs scroll horizontally.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr"/>
+          <t>verified (no change needed)</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Deferred — desktop is primary use case.</t>
-        </is>
-      </c>
-      <c r="K54" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M54" s="3" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4258,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -4272,33 +4268,37 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Full mobile pass: hamburger nav, single-column stacking, ≥44px tap targets, swipe sub-tabs, condensed tables.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr"/>
+          <t>5 min after answer</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Win: -671 lines.</t>
+        </is>
+      </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Deferred indefinitely.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K55" s="14" t="inlineStr">
@@ -4581,13 +4581,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" s="18" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -4622,10 +4622,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4657,10 +4657,10 @@
         <v>17</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" s="23" t="n">
         <v>57</v>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="75" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -1028,39 +1028,35 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Biggest lever for next perf sprint.</t>
-        </is>
-      </c>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1074,13 +1070,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -1095,30 +1091,34 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
+          <t>Caveat: exploratory research, not config-tuning.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+        </is>
+      </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1153,34 +1153,30 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
-        </is>
-      </c>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1194,13 +1190,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>MOD-2</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1210,32 +1206,32 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr"/>
@@ -1258,45 +1254,49 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1310,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1326,39 +1326,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1 min</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Win: -X lines.</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1366,11 +1354,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
+      <c r="N12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="n">
@@ -3008,13 +2992,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
+    <row r="37" ht="135" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -3024,37 +3008,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3069,12 +3053,12 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>54c6f218d</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3068,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -3094,37 +3078,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3134,27 +3118,27 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="75" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -3164,37 +3148,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3209,22 +3193,22 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="75" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -3239,17 +3223,17 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3259,12 +3243,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3284,17 +3268,17 @@
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -3304,22 +3288,22 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3329,12 +3313,12 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3349,22 +3333,22 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="90" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="75" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3374,37 +3358,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3414,27 +3398,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="90" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -3444,37 +3428,37 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3484,27 +3468,27 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -3514,37 +3498,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3559,60 +3543,64 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="60" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-3</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr"/>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Trivial.</t>
+        </is>
+      </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3625,22 +3613,22 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="75" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -3655,17 +3643,17 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3675,14 +3663,10 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3695,22 +3679,22 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="75" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -3720,22 +3704,22 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3745,10 +3729,14 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr"/>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3761,22 +3749,22 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="75" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -3786,22 +3774,22 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3811,14 +3799,10 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3831,22 +3815,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="60" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="75" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -3856,37 +3840,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3896,17 +3880,17 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3900,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -3931,32 +3915,32 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -3976,7 +3960,7 @@
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3970,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4001,32 +3985,32 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -4046,7 +4030,7 @@
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4040,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4071,32 +4055,32 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -4106,67 +4090,67 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>OPS-5</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Win: persistence works; no silent overwrites.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -4179,10 +4163,14 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4180,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -4207,32 +4195,32 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -4248,7 +4236,7 @@
       <c r="M54" s="3" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -4258,59 +4246,63 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K55" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4312,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -4330,37 +4322,37 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K56" s="14" t="inlineStr">
@@ -4382,109 +4374,109 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K57" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K57" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="3" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="90" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="45" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Data / Universe</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>$$ + 1 day</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K58" s="15" t="inlineStr">
@@ -4492,13 +4484,75 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+      <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K59" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr"/>
+      <c r="N59" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -4562,10 +4616,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="18" t="n">
         <v>12</v>
@@ -4600,13 +4654,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>8</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -4660,10 +4714,10 @@
         <v>25</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,11 +54,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
@@ -74,10 +69,6 @@
     <font>
       <b val="1"/>
       <color rgb="00000000"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -100,7 +91,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -130,11 +121,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE9B5"/>
       </patternFill>
     </fill>
     <fill>
@@ -179,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -214,34 +200,30 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1418,13 +1400,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="75" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1434,49 +1416,57 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Concerning: 30+ min into backtest, still 0 BUYs across 5 months simulated. Likely needs per-band kill (TC at score 60-79 only) instead of full kill.</t>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
         </is>
       </c>
     </row>
@@ -1486,113 +1476,137 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>OPERATING-MINDSET</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr"/>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
+        </is>
+      </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Initial CSS shipped 2026-05-10. May need follow-up for specific tabs (Portfolio, Tracking) once tested live.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="75" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="105" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr"/>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+        </is>
+      </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Hamburger nav + swipe gestures NOT yet — desktop-style topnav with horizontal scroll works on phones. Revisit only if user reports usability issue.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>0574c60d4</t>
+        </is>
+      </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
         </is>
       </c>
     </row>
@@ -1602,73 +1616,77 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step1</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Wilson LB clears 40% threshold. Don't enable until subtype investigation done.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>grep -A20 'pullback_bull_701' config/config.json → _validations entry present with n=134 wr_lb=0.446. _enabled stays false.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="75" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1678,40 +1696,40 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1723,22 +1741,22 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1748,67 +1766,67 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="105" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1818,22 +1836,22 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1843,15 +1861,15 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
+          <t>Pure additive. Does not affect existing analysis.</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1863,22 +1881,22 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1888,40 +1906,40 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1933,12 +1951,12 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1966,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1958,40 +1976,40 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="inlineStr">
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2003,22 +2021,22 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2028,40 +2046,40 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr">
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2073,12 +2091,12 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2106,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2098,67 +2116,67 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2168,22 +2186,22 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2193,15 +2211,15 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
-        </is>
-      </c>
-      <c r="K25" s="12" t="inlineStr">
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2213,22 +2231,22 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2238,40 +2256,40 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
-        </is>
-      </c>
-      <c r="K26" s="12" t="inlineStr">
+          <t>Existing positions unaffected (exits run via separate paths).</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2283,12 +2301,12 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -2298,50 +2316,50 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
-        </is>
-      </c>
-      <c r="K27" s="12" t="inlineStr">
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2353,12 +2371,12 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
         </is>
       </c>
     </row>
@@ -2368,147 +2386,147 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>CLEAN-1</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
-        </is>
-      </c>
-      <c r="K28" s="12" t="inlineStr">
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="90" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>CLEAN-3</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
-        </is>
-      </c>
-      <c r="K29" s="12" t="inlineStr">
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -2518,40 +2536,40 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
-        </is>
-      </c>
-      <c r="K30" s="12" t="inlineStr">
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2563,12 +2581,12 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2596,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -2588,57 +2606,57 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
-        </is>
-      </c>
-      <c r="K31" s="12" t="inlineStr">
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2666,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -2658,40 +2676,36 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
-        </is>
-      </c>
-      <c r="K32" s="12" t="inlineStr">
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2703,22 +2717,22 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="75" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -2728,67 +2742,63 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
-        </is>
-      </c>
-      <c r="K33" s="12" t="inlineStr">
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -2798,40 +2808,40 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
-        </is>
-      </c>
-      <c r="K34" s="12" t="inlineStr">
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2843,12 +2853,12 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2868,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -2873,35 +2883,35 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr">
+          <t>Trivial fix; verify no race with first user interaction.</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2913,22 +2923,22 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="135" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -2943,62 +2953,62 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
-        </is>
-      </c>
-      <c r="K36" s="12" t="inlineStr">
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="135" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -3008,40 +3018,40 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
-        </is>
-      </c>
-      <c r="K37" s="12" t="inlineStr">
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3053,12 +3063,12 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3078,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -3078,67 +3088,67 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
-        </is>
-      </c>
-      <c r="K38" s="12" t="inlineStr">
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="120" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -3148,47 +3158,47 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
-        </is>
-      </c>
-      <c r="K39" s="12" t="inlineStr">
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -3198,7 +3208,7 @@
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3261,7 @@
           <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr">
+      <c r="K40" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3321,7 +3331,7 @@
           <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
-      <c r="K41" s="12" t="inlineStr">
+      <c r="K41" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3391,7 +3401,7 @@
           <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
-      <c r="K42" s="12" t="inlineStr">
+      <c r="K42" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3461,7 +3471,7 @@
           <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr">
+      <c r="K43" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3531,7 +3541,7 @@
           <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr">
+      <c r="K44" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3601,7 +3611,7 @@
           <t>Trivial.</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
+      <c r="K45" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3667,7 +3677,7 @@
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="12" t="inlineStr">
+      <c r="K46" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3737,7 +3747,7 @@
           <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr">
+      <c r="K47" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3803,7 +3813,7 @@
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="12" t="inlineStr">
+      <c r="K48" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3873,7 +3883,7 @@
           <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr">
+      <c r="K49" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3943,7 +3953,7 @@
           <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr">
+      <c r="K50" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4013,7 +4023,7 @@
           <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr">
+      <c r="K51" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4083,7 +4093,7 @@
           <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
-      <c r="K52" s="12" t="inlineStr">
+      <c r="K52" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4153,7 +4163,7 @@
           <t>Trivial CLI wrapper.</t>
         </is>
       </c>
-      <c r="K53" s="12" t="inlineStr">
+      <c r="K53" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4183,7 +4193,7 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4223,7 +4233,7 @@
           <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
-      <c r="K54" s="12" t="inlineStr">
+      <c r="K54" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4249,7 +4259,7 @@
           <t>I4</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4289,7 +4299,7 @@
           <t>7 backup dirs present, latest 2026-05-08.</t>
         </is>
       </c>
-      <c r="K55" s="12" t="inlineStr">
+      <c r="K55" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4355,7 +4365,7 @@
           <t>Standard data-migration retention practice.</t>
         </is>
       </c>
-      <c r="K56" s="14" t="inlineStr">
+      <c r="K56" s="13" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
@@ -4417,7 +4427,7 @@
           <t>Don't pre-implement.</t>
         </is>
       </c>
-      <c r="K57" s="14" t="inlineStr">
+      <c r="K57" s="13" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
@@ -4479,7 +4489,7 @@
           <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
-      <c r="K58" s="15" t="inlineStr">
+      <c r="K58" s="14" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
@@ -4501,7 +4511,7 @@
           <t>H1</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4541,7 +4551,7 @@
           <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
         </is>
       </c>
-      <c r="K59" s="15" t="inlineStr">
+      <c r="K59" s="14" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
@@ -4569,7 +4579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4580,143 +4590,124 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="18" t="n">
+      <c r="C2" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="18" t="n">
+      <c r="E2" s="17" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="n">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="18" t="n">
+      <c r="C5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="18" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="n">
-        <v>12</v>
-      </c>
-      <c r="C4" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="18" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
+      <c r="D5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>2</v>
+      <c r="E5" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B6" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C6" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D6" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E6" s="21" t="n">
         <v>58</v>
       </c>
     </row>
@@ -4740,153 +4731,153 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>What it does</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py list</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>Show all items grouped by status</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py list --open</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Show only OPEN / IN_PROGRESS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py done &lt;id&gt;</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Mark item DONE (auto-fills today's date + HEAD commit)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py done &lt;id&gt; --commit abc123 --date 2026-05-09</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Mark DONE with explicit commit/date</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py status &lt;id&gt; IN_PROGRESS</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Set arbitrary status (OPEN/IN_PROGRESS/DONE/DEFERRED/REJECTED)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py add NEW-ID P1 "Section" "Item title" "What" "How"</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Add a new item to the registry</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py xlsx</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Regenerate this Excel from data/open_items.json</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>edit data/open_items.json directly, then run xlsx</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Free-form edits — works too</t>
         </is>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009C5700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
@@ -69,6 +74,10 @@
     <font>
       <b val="1"/>
       <color rgb="00000000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -91,7 +100,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +130,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE9B5"/>
       </patternFill>
     </fill>
     <fill>
@@ -165,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -200,30 +214,34 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1178,45 +1196,49 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1230,13 +1252,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="75" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1246,39 +1268,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1 min</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Win: -X lines.</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1286,19 +1296,15 @@
       </c>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="75" customHeight="1">
+      <c r="N11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1308,27 +1314,39 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Defer until next major refactor.</t>
+        </is>
+      </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1336,20 +1354,24 @@
       </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1359,44 +1381,44 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Defer until next major refactor.</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1471,7 @@
           <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K14" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1519,7 +1541,7 @@
           <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1589,7 +1611,7 @@
           <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1659,7 +1681,7 @@
           <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="K17" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1729,7 +1751,7 @@
           <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1799,7 +1821,7 @@
           <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="K19" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1869,7 +1891,7 @@
           <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K20" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1939,7 +1961,7 @@
           <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K21" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2009,7 +2031,7 @@
           <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K22" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2079,7 +2101,7 @@
           <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2149,7 +2171,7 @@
           <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2219,7 +2241,7 @@
           <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2289,7 +2311,7 @@
           <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="K26" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2359,7 +2381,7 @@
           <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K27" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2429,7 +2451,7 @@
           <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2499,7 +2521,7 @@
           <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K29" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2569,7 +2591,7 @@
           <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="K30" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2639,7 +2661,7 @@
           <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="K31" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2705,7 +2727,7 @@
           <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2771,7 +2793,7 @@
           <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="K33" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2841,7 +2863,7 @@
           <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="K34" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2911,7 +2933,7 @@
           <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr">
+      <c r="K35" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2981,7 +3003,7 @@
           <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="K36" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3051,7 +3073,7 @@
           <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="K37" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3121,7 +3143,7 @@
           <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr">
+      <c r="K38" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3191,7 +3213,7 @@
           <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr">
+      <c r="K39" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3261,7 +3283,7 @@
           <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr">
+      <c r="K40" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3331,7 +3353,7 @@
           <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="K41" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3401,7 +3423,7 @@
           <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
-      <c r="K42" s="11" t="inlineStr">
+      <c r="K42" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3471,7 +3493,7 @@
           <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
+      <c r="K43" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3541,7 +3563,7 @@
           <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
-      <c r="K44" s="11" t="inlineStr">
+      <c r="K44" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3611,7 +3633,7 @@
           <t>Trivial.</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="K45" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3677,7 +3699,7 @@
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="11" t="inlineStr">
+      <c r="K46" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3747,7 +3769,7 @@
           <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
+      <c r="K47" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3813,7 +3835,7 @@
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="11" t="inlineStr">
+      <c r="K48" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3883,7 +3905,7 @@
           <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
-      <c r="K49" s="11" t="inlineStr">
+      <c r="K49" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3953,7 +3975,7 @@
           <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
-      <c r="K50" s="11" t="inlineStr">
+      <c r="K50" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4023,7 +4045,7 @@
           <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
-      <c r="K51" s="11" t="inlineStr">
+      <c r="K51" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4093,7 +4115,7 @@
           <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
-      <c r="K52" s="11" t="inlineStr">
+      <c r="K52" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4163,7 +4185,7 @@
           <t>Trivial CLI wrapper.</t>
         </is>
       </c>
-      <c r="K53" s="11" t="inlineStr">
+      <c r="K53" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4193,7 +4215,7 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4233,7 +4255,7 @@
           <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
-      <c r="K54" s="11" t="inlineStr">
+      <c r="K54" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4259,7 +4281,7 @@
           <t>I4</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4299,7 +4321,7 @@
           <t>7 backup dirs present, latest 2026-05-08.</t>
         </is>
       </c>
-      <c r="K55" s="11" t="inlineStr">
+      <c r="K55" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4365,7 +4387,7 @@
           <t>Standard data-migration retention practice.</t>
         </is>
       </c>
-      <c r="K56" s="13" t="inlineStr">
+      <c r="K56" s="14" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
@@ -4427,7 +4449,7 @@
           <t>Don't pre-implement.</t>
         </is>
       </c>
-      <c r="K57" s="13" t="inlineStr">
+      <c r="K57" s="14" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
@@ -4489,7 +4511,7 @@
           <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
-      <c r="K58" s="14" t="inlineStr">
+      <c r="K58" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
@@ -4511,7 +4533,7 @@
           <t>H1</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -4551,7 +4573,7 @@
           <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
         </is>
       </c>
-      <c r="K59" s="14" t="inlineStr">
+      <c r="K59" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
@@ -4579,7 +4601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4590,124 +4612,143 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="D2" s="17" t="n">
+      <c r="C2" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="17" t="n">
-        <v>12</v>
+      <c r="E2" s="18" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>19</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B7" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C7" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D7" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E7" s="23" t="n">
         <v>58</v>
       </c>
     </row>
@@ -4731,153 +4772,153 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>What it does</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py list</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>Show all items grouped by status</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py list --open</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Show only OPEN / IN_PROGRESS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py done &lt;id&gt;</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Mark item DONE (auto-fills today's date + HEAD commit)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py done &lt;id&gt; --commit abc123 --date 2026-05-09</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Mark DONE with explicit commit/date</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py status &lt;id&gt; IN_PROGRESS</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Set arbitrary status (OPEN/IN_PROGRESS/DONE/DEFERRED/REJECTED)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py add NEW-ID P1 "Section" "Item title" "What" "How"</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Add a new item to the registry</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py xlsx</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Regenerate this Excel from data/open_items.json</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>edit data/open_items.json directly, then run xlsx</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Free-form edits — works too</t>
         </is>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -970,32 +970,32 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr"/>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -1033,30 +1033,34 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
+          <t>Caveat: exploratory research, not config-tuning.</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+        </is>
+      </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1076,7 +1080,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -1091,34 +1095,30 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
-        </is>
-      </c>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1132,51 +1132,55 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr"/>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1190,13 +1194,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1206,39 +1210,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1 min</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Win: -X lines.</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1246,19 +1238,15 @@
       </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="75" customHeight="1">
+      <c r="N10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1268,27 +1256,39 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Defer until next major refactor.</t>
+        </is>
+      </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1296,20 +1296,24 @@
       </c>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1319,116 +1323,124 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Defer until next major refactor.</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1438,22 +1450,22 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1463,12 +1475,12 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1478,27 +1490,27 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="105" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1508,22 +1520,22 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1533,12 +1545,12 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1548,27 +1560,27 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="105" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1578,37 +1590,37 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1623,22 +1635,22 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1653,32 +1665,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1698,7 +1710,7 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1720,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1723,17 +1735,17 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1743,12 +1755,12 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1768,17 +1780,17 @@
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1788,37 +1800,37 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1833,22 +1845,22 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1858,22 +1870,22 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1883,12 +1895,12 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1903,12 +1915,12 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1930,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1933,32 +1945,32 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -1973,22 +1985,22 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1998,37 +2010,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2043,22 +2055,22 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="90" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2068,37 +2080,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2108,27 +2120,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2138,37 +2150,37 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2178,17 +2190,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2210,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2213,17 +2225,17 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2233,12 +2245,12 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2253,12 +2265,12 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -2268,47 +2280,47 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2323,12 +2335,12 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2350,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2348,37 +2360,37 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2388,27 +2400,27 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -2423,32 +2435,32 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2468,17 +2480,17 @@
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -2488,37 +2500,37 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2528,27 +2540,27 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -2558,22 +2570,22 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2583,12 +2595,12 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2603,22 +2615,22 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="90" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -2628,37 +2640,33 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2668,27 +2676,27 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="90" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="75" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -2703,28 +2711,28 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>8-12 hrs</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2744,17 +2752,17 @@
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="75" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -2764,33 +2772,37 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr"/>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+        </is>
+      </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2800,17 +2812,17 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2832,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -2835,32 +2847,32 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2875,22 +2887,22 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="120" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -2905,32 +2917,32 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -2940,17 +2952,17 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>5df6b9ef8</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
         </is>
       </c>
     </row>
@@ -4648,13 +4660,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>3</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -4686,13 +4698,13 @@
         <v>13</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>8</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -1194,13 +1194,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="75" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1210,27 +1210,39 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Defer until next major refactor.</t>
+        </is>
+      </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1238,20 +1250,24 @@
       </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1261,116 +1277,124 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Defer until next major refactor.</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1">
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1380,22 +1404,22 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1405,12 +1429,12 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1420,27 +1444,27 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="90" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="105" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1450,22 +1474,22 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1475,12 +1499,12 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1490,27 +1514,27 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="105" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1520,37 +1544,37 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1565,22 +1589,22 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1595,32 +1619,32 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1640,7 +1664,7 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1674,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1665,17 +1689,17 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1685,12 +1709,12 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1710,17 +1734,17 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1730,37 +1754,37 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1775,22 +1799,22 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1800,22 +1824,22 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1825,12 +1849,12 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1845,12 +1869,12 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1884,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1875,32 +1899,32 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1915,22 +1939,22 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1940,37 +1964,37 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -1985,22 +2009,22 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2010,37 +2034,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2050,27 +2074,27 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2080,37 +2104,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2120,17 +2144,17 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2164,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2155,17 +2179,17 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2175,12 +2199,12 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2195,12 +2219,12 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -2210,47 +2234,47 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2265,12 +2289,12 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2304,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -2290,37 +2314,37 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2330,27 +2354,27 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2365,32 +2389,32 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2410,17 +2434,17 @@
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -2430,37 +2454,37 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2470,27 +2494,27 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -2500,22 +2524,22 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2525,12 +2549,12 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2545,22 +2569,22 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -2570,37 +2594,33 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2610,27 +2630,27 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="90" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="75" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -2645,28 +2665,28 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>8-12 hrs</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2686,17 +2706,17 @@
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="75" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -2706,33 +2726,37 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr"/>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+        </is>
+      </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2742,17 +2766,17 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2786,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -2777,32 +2801,32 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2817,22 +2841,22 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="120" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -2847,32 +2871,32 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2882,27 +2906,27 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="120" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="135" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -2917,32 +2941,32 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -2957,22 +2981,22 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>5df6b9ef8</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="135" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -2982,37 +3006,37 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3027,12 +3051,12 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3066,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -3052,37 +3076,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3092,27 +3116,27 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="120" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -3122,37 +3146,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3162,7 +3186,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3172,17 +3196,17 @@
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="120" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="75" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -3192,37 +3216,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3232,27 +3256,27 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -3267,17 +3291,17 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3287,12 +3311,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3312,17 +3336,17 @@
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="75" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -3332,22 +3356,22 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3357,12 +3381,12 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3377,22 +3401,22 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="90" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3402,37 +3426,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3442,27 +3466,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="90" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -3472,37 +3496,37 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3512,27 +3536,27 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -3542,37 +3566,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3587,64 +3611,60 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Trivial.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr"/>
       <c r="K45" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3657,22 +3677,22 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="60" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="75" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -3687,17 +3707,17 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3707,10 +3727,14 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr"/>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3723,22 +3747,22 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="75" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -3748,22 +3772,22 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3773,14 +3797,10 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3793,22 +3813,22 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="45" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="75" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -3818,22 +3838,22 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3843,10 +3863,14 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr"/>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>User can still bypass with --no-verify in emergencies.</t>
+        </is>
+      </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3859,22 +3883,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="75" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -3884,37 +3908,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3924,17 +3948,17 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3968,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -3959,32 +3983,32 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -4004,7 +4028,7 @@
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4038,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4029,32 +4053,32 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -4074,7 +4098,7 @@
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4108,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4099,32 +4123,32 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -4134,27 +4158,27 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="60" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="150" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -4164,37 +4188,29 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>Win: fast iteration on report templates.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -4204,17 +4220,17 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>b02935ad8</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
         </is>
       </c>
     </row>
@@ -4663,10 +4679,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -4701,10 +4717,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2298,13 +2298,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -2314,37 +2314,37 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2359,22 +2359,22 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="90" customHeight="1">
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2384,37 +2384,37 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -2454,37 +2454,37 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -2524,37 +2524,37 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2564,27 +2564,27 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="90" customHeight="1">
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -2594,33 +2594,37 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr"/>
+          <t>10 min after answer</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Win: -158 lines + clearer docs.</t>
+        </is>
+      </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2635,22 +2639,22 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="75" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="90" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -2660,33 +2664,37 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr"/>
+          <t>30 min after answers</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~3-5K lines if mostly stale.</t>
+        </is>
+      </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2701,12 +2709,12 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2724,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -2726,37 +2734,37 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2771,22 +2779,22 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -2796,37 +2804,37 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2841,22 +2849,22 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="120" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -2866,37 +2874,33 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>Win: -100ms FCP.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2911,22 +2915,22 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="135" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="75" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -2936,37 +2940,33 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -2981,22 +2981,22 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -3006,37 +3006,37 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3046,27 +3046,27 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -3076,37 +3076,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -3146,37 +3146,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="75" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="135" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -3216,37 +3216,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3256,17 +3256,17 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -3286,37 +3286,37 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3326,27 +3326,27 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="75" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -3356,37 +3356,37 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3401,22 +3401,22 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="90" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3426,37 +3426,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="60" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="75" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -3496,22 +3496,22 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3541,22 +3541,22 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -3566,37 +3566,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3611,47 +3611,47 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="60" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="75" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3661,10 +3661,14 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr"/>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+        </is>
+      </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3677,62 +3681,62 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="90" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3742,52 +3746,52 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3797,10 +3801,14 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr"/>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+        </is>
+      </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3813,62 +3821,62 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="75" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-3</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -3883,12 +3891,12 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3906,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -3908,39 +3916,35 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr"/>
       <c r="K49" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3948,27 +3952,27 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="60" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="75" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -3978,37 +3982,37 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: clear activation procedure before flipping live.</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -4018,27 +4022,27 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="60" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4048,39 +4052,35 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr"/>
       <c r="K51" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4088,27 +4088,27 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="60" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="75" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4118,37 +4118,37 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -4163,22 +4163,22 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="150" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -4188,29 +4188,37 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
+        </is>
+      </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -4225,62 +4233,62 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>b02935ad8</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C54" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>OPS-3</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: persistence works; no silent overwrites.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -4290,63 +4298,67 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>OPS-4</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -4356,23 +4368,27 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -4382,59 +4398,67 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K56" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="3" t="inlineStr"/>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="150" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -4449,44 +4473,44 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>hours-days each</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K57" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="3" t="inlineStr"/>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>cf30df858</t>
+        </is>
+      </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
         </is>
       </c>
     </row>
@@ -4496,69 +4520,73 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K58" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr"/>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="90" customHeight="1">
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -4568,51 +4596,303 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Data / Universe</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>$$ + 1 day</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K59" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr">
+        <is>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Code Cleanup (DEFERRED)</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>5 min after answer</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Win: -671 lines.</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K60" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="3" t="inlineStr"/>
+      <c r="N60" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>hours-days each</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Win varies; defer until PERF-7 measured.</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K62" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K63" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -4714,13 +4994,13 @@
         <v>13</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>9</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -4771,13 +5051,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7" s="23" t="n">
         <v>13</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -706,13 +706,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -727,32 +727,32 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Output: cache/portfolio_backtest_250d_*.json.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -774,47 +774,47 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>OPS-1</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Win: cleaner repo.</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Start by mid-morning Sunday so it finishes before Monday's 1am scan.</t>
+          <t>Calendar reminder for 2026-05-16.</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -836,49 +836,45 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>QUANT-3</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
-        </is>
-      </c>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -892,13 +888,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -908,37 +904,37 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Win: cleaner repo.</t>
+          <t>Caveat: exploratory research, not config-tuning.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Calendar reminder for 2026-05-16.</t>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -954,13 +950,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -975,27 +971,27 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr"/>
@@ -1012,53 +1008,53 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
+          <t>Win: -X lines.</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+          <t>Couples with OPS-1.</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1080,45 +1076,49 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>MOD-1</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Defer until next major refactor.</t>
+        </is>
+      </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1132,127 +1132,135 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="90" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1 min</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Win: -X lines.</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Defer until next major refactor.</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
         </is>
       </c>
     </row>
@@ -1262,69 +1270,77 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>OPERATING-MINDSET</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="75" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="105" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1334,22 +1350,22 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1359,12 +1375,12 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1379,22 +1395,22 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1404,37 +1420,37 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1444,27 +1460,27 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="105" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1474,37 +1490,37 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1519,22 +1535,22 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1549,32 +1565,32 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1594,17 +1610,17 @@
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1619,32 +1635,32 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1654,27 +1670,27 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1689,32 +1705,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1724,17 +1740,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4969,7 @@
         </is>
       </c>
       <c r="B2" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="18" t="n">
         <v>4</v>
@@ -4962,7 +4978,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -4991,7 +5007,7 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="18" t="n">
         <v>24</v>
@@ -5000,7 +5016,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="105" customHeight="1">
+    <row r="17" ht="180" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -3916,51 +3916,47 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
+    <row r="49" ht="105" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-A</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr"/>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+        </is>
+      </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3968,67 +3964,59 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="75" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="105" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-B</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -4038,27 +4026,27 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -4068,22 +4056,22 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4093,7 +4081,7 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
+          <t>Win: future Claude sessions discover new tools.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr"/>
@@ -4109,12 +4097,12 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4112,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -4134,22 +4122,22 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4159,12 +4147,12 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: clear activation procedure before flipping live.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -4179,22 +4167,22 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="60" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="45" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -4204,39 +4192,35 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr"/>
       <c r="K53" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4244,27 +4228,27 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="60" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="75" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -4274,37 +4258,37 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -4314,17 +4298,17 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4318,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -4349,32 +4333,32 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -4394,7 +4378,7 @@
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4388,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -4419,32 +4403,32 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
@@ -4454,27 +4438,27 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="150" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -4484,29 +4468,37 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Win: visibility into RBAC changes.</t>
+        </is>
+      </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
@@ -4521,62 +4513,62 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>OPS-5</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Win: persistence works; no silent overwrites.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -4589,60 +4581,56 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="M58" s="3" t="inlineStr"/>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="150" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>PERF-7b</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>verified (no change needed)</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>Win: confirms infrastructure still healthy.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -4652,13 +4640,17 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>cf30df858</t>
+        </is>
+      </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
         </is>
       </c>
     </row>
@@ -4668,59 +4660,63 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K60" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr"/>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -4730,59 +4726,63 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K61" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -4792,123 +4792,247 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K62" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K62" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="90" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Data / Universe</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>$$ + 1 day</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K63" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K64" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="3" t="inlineStr"/>
+      <c r="N64" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="90" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K65" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr"/>
+      <c r="N65" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -5010,13 +5134,13 @@
         <v>15</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>9</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -5067,13 +5191,13 @@
         <v>17</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="23" t="n">
         <v>13</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -114,17 +114,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -135,6 +130,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE9B5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -208,10 +208,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,7 +233,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -712,47 +712,47 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>OPS-1</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: cleaner repo.</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Calendar reminder for 2026-05-16.</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -774,49 +774,45 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
+          <t>QUANT-3</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Win: cleaner repo.</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Calendar reminder for 2026-05-16.</t>
-        </is>
-      </c>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -830,16 +826,16 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
+          <t>QUANT-5</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -851,30 +847,34 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr"/>
+          <t>Caveat: exploratory research, not config-tuning.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+        </is>
+      </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -894,10 +894,10 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+          <t>QUANT-6</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -909,34 +909,30 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
-        </is>
-      </c>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -950,51 +946,55 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>CLEAN-4</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1008,127 +1008,135 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="90" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1 min</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Win: -X lines.</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Defer until next major refactor.</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
         </is>
       </c>
     </row>
@@ -1138,94 +1146,102 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>OPERATING-MINDSET</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="75" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="105" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1235,12 +1251,12 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -1255,62 +1271,62 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+          <t>Q1-step1</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -1320,67 +1336,67 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="105" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+          <t>Q1-step2</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1395,25 +1411,25 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+          <t>Q1-step3</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1425,32 +1441,32 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1470,20 +1486,20 @@
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+          <t>Q1-step4</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1495,32 +1511,32 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1530,30 +1546,30 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="180" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+          <t>Q1-step5</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1565,32 +1581,32 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1600,30 +1616,30 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+          <t>Q1-step6</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1635,32 +1651,32 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1675,7 +1691,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
@@ -1684,53 +1700,53 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="180" customHeight="1">
+    <row r="17" ht="90" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1740,52 +1756,52 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+          <t>Q1-Fix1</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1795,12 +1811,12 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1815,12 +1831,12 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -1830,10 +1846,10 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+          <t>Q1-Fix3</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1845,32 +1861,32 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1885,62 +1901,62 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1955,62 +1971,62 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+          <t>GATE-1</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2020,67 +2036,67 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2090,17 +2106,17 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2110,10 +2126,10 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -2125,17 +2141,17 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2145,12 +2161,12 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2165,12 +2181,12 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -2180,47 +2196,47 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2235,62 +2251,62 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+          <t>PERF-OPT-1</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2300,17 +2316,17 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -2320,10 +2336,10 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
+          <t>PERF-OPT-2</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2335,22 +2351,22 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2360,7 +2376,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2380,7 +2396,7 @@
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -2390,10 +2406,10 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
+          <t>PERF-OPT-3</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2405,32 +2421,32 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2450,20 +2466,20 @@
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
+          <t>PERF-OPT-4</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2475,32 +2491,32 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2520,7 +2536,7 @@
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
         </is>
       </c>
     </row>
@@ -2530,47 +2546,47 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
+          <t>CLEAN-1</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2585,25 +2601,25 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
+          <t>CLEAN-3</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2615,32 +2631,32 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2660,57 +2676,57 @@
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2720,52 +2736,52 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2775,12 +2791,12 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2795,62 +2811,58 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="90" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
+          <t>MOB-1</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2860,30 +2872,30 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="90" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="75" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
+          <t>MOB-2</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2895,28 +2907,28 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>8-12 hrs</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2936,53 +2948,57 @@
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="75" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
+          <t>PERF-4</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+        </is>
+      </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -2992,17 +3008,17 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -3012,10 +3028,10 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
+          <t>PERF-5</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3027,32 +3043,32 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3067,25 +3083,25 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="120" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
+          <t>PERF-6</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3097,32 +3113,32 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3132,30 +3148,30 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="120" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="135" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
+          <t>PERF-7</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3167,32 +3183,32 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3207,62 +3223,62 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="135" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
+          <t>QUANT-4</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3277,12 +3293,12 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
         </is>
       </c>
     </row>
@@ -3292,47 +3308,47 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3342,67 +3358,67 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="120" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
+          <t>A5-followup</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3412,7 +3428,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3422,57 +3438,57 @@
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="120" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="75" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3482,30 +3498,30 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3517,17 +3533,17 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3537,12 +3553,12 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3562,42 +3578,42 @@
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3607,12 +3623,12 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3627,62 +3643,62 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="90" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
@@ -3692,67 +3708,67 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="90" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3762,67 +3778,67 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="60" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
+          <t>MOD-3</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
@@ -3837,25 +3853,25 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="105" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
+          <t>MOD-A</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3867,32 +3883,24 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -3902,17 +3910,17 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
         </is>
       </c>
     </row>
@@ -3922,10 +3930,10 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
+          <t>MOD-B</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -3937,24 +3945,24 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3969,56 +3977,60 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="105" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
-        </is>
-      </c>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4026,30 +4038,30 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="60" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="75" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4061,17 +4073,17 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4081,10 +4093,14 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr"/>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4097,47 +4113,47 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="75" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="45" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4147,14 +4163,10 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr"/>
       <c r="K52" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4167,47 +4179,47 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="75" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
+          <t>F11-followup</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4217,10 +4229,14 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr"/>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>User can still bypass with --no-verify in emergencies.</t>
+        </is>
+      </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4233,62 +4249,62 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="75" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
+          <t>OPS-2</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -4298,17 +4314,17 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -4318,10 +4334,10 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
+          <t>OPS-3</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4333,32 +4349,32 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -4378,7 +4394,7 @@
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -4388,10 +4404,10 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
+          <t>OPS-4</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4403,32 +4419,32 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
@@ -4448,7 +4464,7 @@
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
         </is>
       </c>
     </row>
@@ -4458,10 +4474,10 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
+          <t>OPS-5</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4473,32 +4489,32 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
@@ -4508,67 +4524,59 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="60" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="150" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
+          <t>PERF-7b</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>Win: fast iteration on report templates.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -4578,59 +4586,67 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>cf30df858</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="150" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="135" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
+          <t>MOD-1</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -4645,12 +4661,12 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>42c36ef91</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4811,7 @@
           <t>CLEAN-2</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4857,7 +4873,7 @@
           <t>PERF-8-13</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -4919,7 +4935,7 @@
           <t>Q1-step7</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -5093,16 +5109,16 @@
         </is>
       </c>
       <c r="B2" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="18" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5131,16 +5147,16 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="18" t="n">
         <v>26</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs.</t>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1156,37 +1156,29 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -1201,22 +1193,22 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1226,22 +1218,22 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1251,12 +1243,12 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -1266,27 +1258,27 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="105" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1296,37 +1288,37 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -1341,22 +1333,22 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1371,32 +1363,32 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1416,7 +1408,7 @@
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1418,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1441,17 +1433,17 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1461,12 +1453,12 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1486,17 +1478,17 @@
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1511,32 +1503,32 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1546,27 +1538,27 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="180" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1581,32 +1573,32 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1621,22 +1613,22 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="180" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1651,32 +1643,32 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1691,22 +1683,22 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1716,37 +1708,37 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1756,27 +1748,27 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1786,22 +1778,22 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1811,12 +1803,12 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1831,12 +1823,12 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1838,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1861,32 +1853,32 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1901,22 +1893,22 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -1926,37 +1918,37 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1971,22 +1963,22 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="105" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -1996,37 +1988,29 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>in flight</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2041,12 +2025,12 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2040,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -2066,22 +2050,22 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2091,12 +2075,12 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2111,22 +2095,22 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="90" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2136,37 +2120,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2176,17 +2160,17 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
         </is>
       </c>
     </row>
@@ -2196,47 +2180,47 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2251,62 +2235,62 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2316,27 +2300,27 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2346,37 +2330,37 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2386,17 +2370,17 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2390,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2421,17 +2405,17 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2441,7 +2425,7 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -2466,17 +2450,17 @@
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2491,32 +2475,32 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2536,17 +2520,17 @@
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2556,37 +2540,37 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2601,22 +2585,22 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="90" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2626,37 +2610,37 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2671,22 +2655,22 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2696,37 +2680,37 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2736,27 +2720,27 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2766,37 +2750,37 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2806,27 +2790,27 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2836,33 +2820,37 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr"/>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+        </is>
+      </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2872,27 +2860,27 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="75" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2902,33 +2890,37 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr"/>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+        </is>
+      </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2938,27 +2930,27 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="90" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2968,37 +2960,33 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -3008,27 +2996,27 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="75" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3038,37 +3026,33 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>Win: -50ms FCP.</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3078,27 +3062,27 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="120" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3113,32 +3097,32 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3148,27 +3132,27 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="135" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3183,32 +3167,32 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3218,27 +3202,27 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="120" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3248,22 +3232,22 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3273,12 +3257,12 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3293,22 +3277,22 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="135" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3318,37 +3302,37 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3358,27 +3342,27 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="120" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="75" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3388,37 +3372,29 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>shipped (DRAFT)</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3433,22 +3409,22 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="75" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3458,37 +3434,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3498,17 +3474,17 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3494,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3528,37 +3504,37 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3573,22 +3549,22 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="75" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="120" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3598,37 +3574,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3638,27 +3614,27 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="90" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="75" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3668,37 +3644,37 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
@@ -3708,17 +3684,17 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3704,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3738,22 +3714,22 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3763,12 +3739,12 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3783,22 +3759,22 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="75" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3808,37 +3784,37 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
@@ -3853,22 +3829,22 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="105" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="90" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3878,29 +3854,37 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>shipped (additive only)</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+        </is>
+      </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -3915,12 +3899,12 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3914,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3940,29 +3924,29 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3977,12 +3961,12 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
         </is>
       </c>
     </row>
@@ -3992,32 +3976,32 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4027,10 +4011,14 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr"/>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+        </is>
+      </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4043,62 +4031,62 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="75" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-3</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -4113,60 +4101,56 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="105" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-A</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr"/>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+        </is>
+      </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4174,67 +4158,59 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="75" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="105" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-B</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -4244,17 +4220,17 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4240,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -4274,39 +4250,35 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4314,27 +4286,27 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="60" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="75" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -4344,37 +4316,37 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: clear activation procedure before flipping live.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -4384,27 +4356,27 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="60" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -4414,39 +4386,35 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4454,27 +4422,27 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="75" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -4484,37 +4452,37 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
@@ -4529,22 +4497,22 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="150" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
@@ -4554,29 +4522,37 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
+        </is>
+      </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -4591,22 +4567,22 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="135" customHeight="1">
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -4616,37 +4592,37 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -4661,62 +4637,62 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>OPS-4</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Win: persistence works; no silent overwrites.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K60" s="12" t="inlineStr">
@@ -4726,63 +4702,67 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>OPS-5</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr">
@@ -4795,20 +4775,24 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="150" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -4818,59 +4802,59 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>5 min after answer</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K62" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="3" t="inlineStr"/>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>cf30df858</t>
+        </is>
+      </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="135" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -4880,49 +4864,57 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K63" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="3" t="inlineStr"/>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>42c36ef91</t>
+        </is>
+      </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
         </is>
       </c>
     </row>
@@ -4932,69 +4924,73 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K64" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr"/>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="90" customHeight="1">
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -5004,51 +5000,303 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Data / Universe</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>$$ + 1 day</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K65" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr">
+        <is>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Code Cleanup (DEFERRED)</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>5 min after answer</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Win: -671 lines.</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K66" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="3" t="inlineStr"/>
+      <c r="N66" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>hours-days each</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Win varies; defer until PERF-7 measured.</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K67" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="45" customHeight="1">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K68" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr"/>
+      <c r="N68" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="90" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K69" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -5147,16 +5395,16 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>10</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
@@ -5204,16 +5452,16 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="23" t="n">
         <v>13</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1218,37 +1218,37 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>CRITICAL — system was unable to backtest</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -1263,22 +1263,22 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="105" customHeight="1">
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -1328,27 +1328,27 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="105" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1358,37 +1358,37 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1428,37 +1428,37 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1468,27 +1468,27 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1503,32 +1503,32 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1548,17 +1548,17 @@
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1573,32 +1573,32 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1608,27 +1608,27 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="180" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1678,27 +1678,27 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1713,32 +1713,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="90" customHeight="1">
+    <row r="18" ht="180" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1778,37 +1778,37 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1818,17 +1818,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1848,37 +1848,37 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1888,27 +1888,27 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -1918,37 +1918,37 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1963,22 +1963,22 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="105" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -1988,29 +1988,37 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+        </is>
+      </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2020,27 +2028,27 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -2050,37 +2058,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2095,22 +2103,22 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="90" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="105" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2120,37 +2128,29 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>in flight</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -2190,22 +2190,22 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="90" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2260,37 +2260,37 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2300,67 +2300,67 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>VARIANT-F</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>High — addresses #1 PF drag</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2370,67 +2370,67 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>f0a66543e</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2440,67 +2440,67 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2510,27 +2510,27 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2540,37 +2540,37 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2580,27 +2580,27 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2680,37 +2680,37 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="90" customHeight="1">
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2750,37 +2750,37 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2795,22 +2795,22 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2820,37 +2820,37 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2860,17 +2860,17 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2890,37 +2890,37 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2930,17 +2930,17 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2960,33 +2960,37 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
+          <t>30 min after answers</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~3-5K lines if mostly stale.</t>
+        </is>
+      </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -3001,22 +3005,22 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="75" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3026,33 +3030,37 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr"/>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+        </is>
+      </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3062,27 +3070,27 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3092,37 +3100,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3137,22 +3145,22 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="90" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3162,37 +3170,33 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>Win: -50ms FCP.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3202,27 +3206,27 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="120" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="75" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3232,37 +3236,33 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>Win: -100ms FCP.</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3277,22 +3277,22 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="135" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3302,22 +3302,22 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>Phase 1 shipped 2026-05-10. Phase 2 deferred: real PNG icons, service worker, swipe-to-action.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3347,22 +3347,22 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="75" customHeight="1">
+          <t>On iPad open https://trade.mystockholding.com/v2/ipad/dashboard.html. Landscape: 2-pane split. Portrait: full-width list with detail-on-tap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3372,29 +3372,37 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+        </is>
+      </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3404,27 +3412,27 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="60" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="45" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3434,37 +3442,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3474,27 +3482,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="60" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="120" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3504,37 +3512,37 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3544,27 +3552,27 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="120" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="135" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3574,37 +3582,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3619,12 +3627,12 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3642,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3644,37 +3652,29 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3714,37 +3714,37 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3754,27 +3754,27 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="75" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3784,37 +3784,37 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
@@ -3829,22 +3829,22 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="90" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="120" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3854,37 +3854,37 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -3899,22 +3899,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="105" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="75" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3924,29 +3924,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+        </is>
+      </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3956,17 +3964,17 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3984,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3986,22 +3994,22 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4011,12 +4019,12 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -4031,22 +4039,22 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="75" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4056,37 +4064,37 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -4101,22 +4109,22 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="105" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="90" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4126,29 +4134,37 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>shipped (additive only)</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+        </is>
+      </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -4163,12 +4179,12 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4194,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4188,29 +4204,29 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -4225,60 +4241,64 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="60" customHeight="1">
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>CONFIG-1</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr"/>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+        </is>
+      </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4286,52 +4306,52 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="75" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4341,12 +4361,12 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -4361,12 +4381,12 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
         </is>
       </c>
     </row>
@@ -4376,45 +4396,49 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-3</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr"/>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Trivial.</t>
+        </is>
+      </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4427,62 +4451,54 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="75" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="105" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-A</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
@@ -4492,67 +4508,59 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="60" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="105" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-B</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -4567,62 +4575,62 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="60" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-2</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Low risk / Medium win (consistency)</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>All reads use ?? fallbacks.</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -4637,64 +4645,60 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="60" customHeight="1">
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>RULE-1</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4707,12 +4711,12 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4726,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -4732,39 +4736,35 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>Trivial CLI wrapper.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr"/>
       <c r="K61" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4777,22 +4777,22 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="150" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="75" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -4802,29 +4802,37 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr">
@@ -4834,27 +4842,27 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="135" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -4864,39 +4872,35 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr"/>
       <c r="K63" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4904,17 +4908,17 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
         </is>
       </c>
     </row>
@@ -4924,47 +4928,47 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>IPAD-2</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Win: persistence works; no silent overwrites.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>Sub-task of IPAD-1.</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr">
@@ -4974,28 +4978,32 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>79fa01a75</t>
+        </is>
+      </c>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="75" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C65" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>F11-followup</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -5005,32 +5013,32 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
@@ -5043,20 +5051,24 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="M65" s="3" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>1e40d30fc</t>
+        </is>
+      </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -5066,59 +5078,67 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K66" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="3" t="inlineStr"/>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+        </is>
+      </c>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -5128,175 +5148,777 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K67" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="3" t="inlineStr"/>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+        </is>
+      </c>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="45" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>OPS-4</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K68" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="3" t="inlineStr"/>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+        </is>
+      </c>
+      <c r="K68" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="90" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
+          <t>OPS-5</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Operational Hygiene</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Backtest report manual 'regen' button</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N69" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="150" customHeight="1">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>PERF-7b</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N70" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="135" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>MOD-1</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Scanner deep refactor</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N71" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Verify backtest persistence (cb1f5a010)</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Win: persistence works; no silent overwrites.</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr"/>
+      <c r="N72" s="8" t="inlineStr">
+        <is>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>verified (no change needed)</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Remove emoji icons from Thesis + Research labels</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr"/>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
+      <c r="N74" s="8" t="inlineStr">
+        <is>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="45" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Code Cleanup (DEFERRED)</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>5 min after answer</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Win: -671 lines.</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K75" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>hours-days each</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Win varies; defer until PERF-7 measured.</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K76" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="3" t="inlineStr"/>
+      <c r="N76" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K77" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="90" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C78" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Data / Universe</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>Russell 1000 historical membership (Sharadar SF1)</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>$$ + 1 day</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
         </is>
       </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
         </is>
       </c>
-      <c r="K69" s="15" t="inlineStr">
+      <c r="K78" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr">
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -5395,16 +6017,16 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -5452,16 +6074,16 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -3286,7 +3286,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
+    <row r="40" ht="135" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 shipped 2026-05-10. Phase 2 deferred: real PNG icons, service worker, swipe-to-action.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>On iPad open https://trade.mystockholding.com/v2/ipad/dashboard.html. Landscape: 2-pane split. Portrait: full-width list with detail-on-tap.</t>
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
         </is>
       </c>
     </row>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -768,13 +768,13 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -789,30 +789,34 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr"/>
+          <t>Caveat: exploratory research, not config-tuning.</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+        </is>
+      </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -832,7 +836,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -847,34 +851,30 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
-        </is>
-      </c>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -888,51 +888,55 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr"/>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -946,137 +950,145 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="135" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1 min</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Win: -X lines.</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="135" customHeight="1">
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1086,37 +1098,29 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
@@ -1126,27 +1130,27 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1156,29 +1160,37 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -1198,17 +1210,17 @@
       </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1218,37 +1230,37 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL — system was unable to backtest</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -1263,22 +1275,22 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="105" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1288,22 +1300,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1313,12 +1325,12 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -1328,27 +1340,27 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="105" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1358,37 +1370,37 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1398,27 +1410,27 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1428,37 +1440,37 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Low / Required</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1468,27 +1480,27 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1503,32 +1515,32 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1548,7 +1560,7 @@
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1570,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1573,17 +1585,17 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1593,12 +1605,12 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1618,17 +1630,17 @@
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1643,32 +1655,32 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1678,27 +1690,27 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="180" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1713,32 +1725,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1753,22 +1765,22 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="180" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1783,32 +1795,32 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1823,22 +1835,22 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1848,37 +1860,37 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1888,27 +1900,27 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -1918,22 +1930,22 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1943,12 +1955,12 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1963,12 +1975,12 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1990,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -1993,32 +2005,32 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2033,22 +2045,22 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="105" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -2058,37 +2070,29 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>shipped (revert candidate)</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2098,27 +2102,27 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2128,29 +2132,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Win: single most important Vinod rule per coaching call.</t>
+        </is>
+      </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2160,27 +2172,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -2190,37 +2202,37 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2230,27 +2242,27 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2260,37 +2272,37 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>High — addresses #1 PF drag</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2305,22 +2317,22 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>f0a66543e</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -2330,37 +2342,37 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2370,17 +2382,17 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2402,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2405,17 +2417,17 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2425,12 +2437,12 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2445,12 +2457,12 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -2460,47 +2472,47 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2515,22 +2527,22 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2540,37 +2552,37 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2580,17 +2592,17 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2612,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2615,22 +2627,22 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -2640,7 +2652,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2660,7 +2672,7 @@
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2682,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2685,32 +2697,32 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2730,17 +2742,17 @@
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2755,32 +2767,32 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2800,7 +2812,7 @@
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2822,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2820,37 +2832,37 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2865,22 +2877,22 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2895,32 +2907,32 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2940,17 +2952,17 @@
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2960,37 +2972,37 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -3000,27 +3012,27 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3030,22 +3042,22 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3055,12 +3067,12 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3075,22 +3087,22 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="90" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3100,37 +3112,33 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3140,27 +3148,27 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="90" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="75" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3175,28 +3183,28 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>8-12 hrs</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3216,17 +3224,17 @@
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="75" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="135" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3236,33 +3244,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr"/>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / High win</t>
+        </is>
+      </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3277,22 +3289,22 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="135" customHeight="1">
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3302,37 +3314,37 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3342,17 +3354,17 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3374,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3377,32 +3389,32 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3417,22 +3429,22 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3447,32 +3459,32 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3482,27 +3494,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="120" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="135" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3517,32 +3529,32 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3557,22 +3569,22 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="135" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3582,37 +3594,29 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3627,22 +3631,22 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="75" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="105" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3652,29 +3656,37 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
@@ -3689,12 +3701,12 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
         </is>
       </c>
     </row>
@@ -5982,13 +5994,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -6020,13 +6032,13 @@
         <v>21</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>11</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -830,51 +830,55 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr"/>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -888,137 +892,145 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="135" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1 min</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Win: -X lines.</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="135" customHeight="1">
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1028,37 +1040,29 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
@@ -1068,27 +1072,27 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1098,29 +1102,37 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
@@ -1140,17 +1152,17 @@
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1160,37 +1172,37 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL — system was unable to backtest</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -1205,22 +1217,22 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="105" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1230,22 +1242,22 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1255,12 +1267,12 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -1270,27 +1282,27 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="105" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1300,37 +1312,37 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -1340,27 +1352,27 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1370,37 +1382,37 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Low / Required</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1410,27 +1422,27 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1445,32 +1457,32 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1490,7 +1502,7 @@
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1512,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1515,17 +1527,17 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1535,12 +1547,12 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1560,17 +1572,17 @@
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1585,32 +1597,32 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1620,27 +1632,27 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="180" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1655,32 +1667,32 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1695,22 +1707,22 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="180" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1725,32 +1737,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1765,22 +1777,22 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1790,37 +1802,37 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1830,27 +1842,27 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1860,22 +1872,22 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1885,12 +1897,12 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1905,12 +1917,12 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1932,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -1935,32 +1947,32 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1975,22 +1987,22 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="105" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2000,37 +2012,29 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>shipped (revert candidate)</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2040,27 +2044,27 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -2070,29 +2074,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Win: single most important Vinod rule per coaching call.</t>
+        </is>
+      </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2102,27 +2114,27 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="90" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2132,37 +2144,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2172,27 +2184,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -2202,37 +2214,37 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>High — addresses #1 PF drag</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2247,22 +2259,22 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>f0a66543e</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2272,37 +2284,37 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2312,17 +2324,17 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2344,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -2347,17 +2359,17 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2367,12 +2379,12 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2387,12 +2399,12 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2414,47 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2457,22 +2469,22 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2482,37 +2494,37 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2522,17 +2534,17 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2554,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2557,22 +2569,22 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2582,7 +2594,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2602,7 +2614,7 @@
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2624,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2627,32 +2639,32 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2672,17 +2684,17 @@
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2697,32 +2709,32 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2742,7 +2754,7 @@
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2764,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2762,37 +2774,37 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2807,22 +2819,22 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="90" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2837,32 +2849,32 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2882,17 +2894,17 @@
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2902,37 +2914,37 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2942,27 +2954,27 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2972,22 +2984,22 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2997,12 +3009,12 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -3017,22 +3029,22 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="90" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3042,37 +3054,33 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3082,27 +3090,27 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="90" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="75" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3117,28 +3125,28 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>8-12 hrs</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3158,17 +3166,17 @@
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="75" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="135" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3178,33 +3186,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr"/>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / High win</t>
+        </is>
+      </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3219,22 +3231,22 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="135" customHeight="1">
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3244,37 +3256,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3284,17 +3296,17 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3316,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3319,32 +3331,32 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3359,22 +3371,22 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="120" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3389,32 +3401,32 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3424,27 +3436,27 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="120" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="135" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3459,32 +3471,32 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3499,22 +3511,22 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="135" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="75" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3524,37 +3536,29 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3569,22 +3573,22 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="75" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="105" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3594,29 +3598,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3631,22 +3643,22 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="105" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3661,32 +3673,32 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
@@ -3701,22 +3713,22 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="60" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="105" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3731,32 +3743,32 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3771,12 +3783,12 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
         </is>
       </c>
     </row>
@@ -5994,13 +6006,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -6032,13 +6044,13 @@
         <v>21</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>11</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4344,13 +4344,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
+    <row r="55" ht="90" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4360,37 +4360,37 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier (BHE spec)</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full BHE spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Low / High (transparency + future-proof)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4430,37 +4430,37 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
@@ -4475,22 +4475,22 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="105" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="45" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4505,24 +4505,32 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
@@ -4532,17 +4540,17 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4560,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4567,24 +4575,24 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -4599,22 +4607,22 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="105" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4624,37 +4632,29 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4694,35 +4694,39 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr"/>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>All reads use ?? fallbacks.</t>
+        </is>
+      </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4735,57 +4739,57 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="60" customHeight="1">
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>RULE-1</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
+          <t>Low risk / Medium win (transparency)</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr"/>
@@ -4796,67 +4800,67 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="75" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="105" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TARGET-SOURCES-P1</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (BHE Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (BHE 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1.5 hrs</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
+          <t>Low (no behavior change)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr">
@@ -4866,27 +4870,27 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -4896,22 +4900,22 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4921,7 +4925,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
+          <t>Win: future Claude sessions discover new tools.</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr"/>
@@ -4937,22 +4941,22 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="75" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -4962,37 +4966,37 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Win: clear activation procedure before flipping live.</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Sub-task of IPAD-1.</t>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr">
@@ -5002,27 +5006,27 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="75" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -5032,22 +5036,22 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5057,14 +5061,10 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr"/>
       <c r="K65" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5077,22 +5077,22 @@
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="60" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -5102,37 +5102,37 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>Sub-task of IPAD-1.</t>
         </is>
       </c>
       <c r="K66" s="12" t="inlineStr">
@@ -5147,22 +5147,22 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>79fa01a75</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="60" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="75" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -5172,37 +5172,37 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K67" s="12" t="inlineStr">
@@ -5212,17 +5212,17 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -5247,32 +5247,32 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K68" s="12" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -5317,32 +5317,32 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K69" s="12" t="inlineStr">
@@ -5352,27 +5352,27 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="150" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -5382,29 +5382,37 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="5" t="inlineStr"/>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Win: visibility into RBAC changes.</t>
+        </is>
+      </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K70" s="12" t="inlineStr">
@@ -5419,22 +5427,22 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="135" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -5444,37 +5452,37 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K71" s="12" t="inlineStr">
@@ -5484,67 +5492,59 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="45" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="150" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C72" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>PERF-7b</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K72" s="12" t="inlineStr">
@@ -5554,63 +5554,67 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M72" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>cf30df858</t>
+        </is>
+      </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="135" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C73" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>MOD-1</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
         </is>
       </c>
       <c r="K73" s="12" t="inlineStr">
@@ -5620,13 +5624,17 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>42c36ef91</t>
+        </is>
+      </c>
       <c r="N73" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5644,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -5646,35 +5654,39 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr"/>
+          <t>Win: persistence works; no silent overwrites.</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5682,17 +5694,13 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr"/>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -5702,59 +5710,63 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K75" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr"/>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -5764,59 +5776,63 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K76" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr"/>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -5826,123 +5842,247 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K77" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K77" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="90" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="45" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Data / Universe</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>$$ + 1 day</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K78" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K78" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="3" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="45" customHeight="1">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K79" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="90" customHeight="1">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -6044,13 +6184,13 @@
         <v>21</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>11</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
@@ -6101,13 +6241,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" s="23" t="n">
         <v>14</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier (BHE spec)</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full BHE spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (BHE Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (BHE 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">

--- a/cache/open_items_2026-05-10.xlsx
+++ b/cache/open_items_2026-05-10.xlsx
@@ -114,12 +114,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -130,11 +135,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE9B5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -208,10 +208,10 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,7 +233,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -706,55 +706,43 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="75" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>TARGET-CAP-10WK</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2 min</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>Win: cleaner repo.</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Calendar reminder for 2026-05-16.</t>
-        </is>
-      </c>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -762,59 +750,55 @@
       </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
+      <c r="N2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+          <t>OPS-1</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
+          <t>Win: cleaner repo.</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+          <t>Calendar reminder for 2026-05-16.</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -830,53 +814,53 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1 min</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Win: -X lines.</t>
+          <t>Caveat: exploratory research, not config-tuning.</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Couples with OPS-1.</t>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -892,247 +876,223 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="135" customHeight="1">
+    <row r="5" ht="75" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+          <t>TARGET-CAP-SWEEP</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2-3 hrs</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Win: catches accidental layout regressions.</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75" customHeight="1">
+      <c r="N5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>Win: -X lines.</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>2c9b9f339</t>
-        </is>
-      </c>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL — system was unable to backtest</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
@@ -1142,17 +1102,17 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>2c9b9f339</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1122,39 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
+          <t>B3-WEEKLY-FIX</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -1217,64 +1169,52 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
+          <t>VARIANT-F-BT</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
-        </is>
-      </c>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1282,19 +1222,15 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -1302,32 +1238,32 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
+          <t>P0-WEEKLY</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1337,12 +1273,12 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Low / Required</t>
+          <t>CRITICAL — system was unable to backtest</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -1357,62 +1293,62 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
+          <t>OPERATING-MINDSET</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1422,67 +1358,67 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="105" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1497,12 +1433,12 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
         </is>
       </c>
     </row>
@@ -1512,47 +1448,47 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
+          <t>IPAD-3</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1562,17 +1498,17 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
         </is>
       </c>
     </row>
@@ -1582,10 +1518,10 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
+          <t>Q1-step1</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1597,32 +1533,32 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1632,30 +1568,30 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="180" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
+          <t>Q1-step2</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1667,32 +1603,32 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1702,17 +1638,17 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1722,10 +1658,10 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
+          <t>Q1-step3</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1737,32 +1673,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1772,67 +1708,67 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="90" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
+          <t>Q1-step4</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1842,67 +1778,67 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="180" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
+          <t>Q1-step5</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1912,17 +1848,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
         </is>
       </c>
     </row>
@@ -1932,47 +1868,47 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
+          <t>Q1-step6</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1982,59 +1918,67 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="105" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+        </is>
+      </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2044,52 +1988,52 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
+          <t>Q1-Fix1</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2099,12 +2043,12 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2119,62 +2063,62 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="90" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
+          <t>Q1-Fix3</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2184,67 +2128,59 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="105" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
+          <t>VAR-F</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>High — addresses #1 PF drag</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2259,12 +2195,12 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
         </is>
       </c>
     </row>
@@ -2274,32 +2210,32 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2309,12 +2245,12 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2329,62 +2265,62 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
+          <t>GATE-1</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2394,69 +2330,57 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="75" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>shipped (diagnosis); pending (fix)</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2464,19 +2388,15 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr"/>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="n">
@@ -2484,47 +2404,47 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>High — addresses #1 PF drag</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2539,62 +2459,62 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>f0a66543e</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">